--- a/research/traditional_assets/database/data/bulgaria/bulgaria_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_auto_truck.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.2359882005899705</v>
+        <v>-0.05765765765765765</v>
       </c>
       <c r="H2">
-        <v>-0.2359882005899705</v>
+        <v>-0.05765765765765765</v>
       </c>
       <c r="I2">
-        <v>-0.5132743362831858</v>
+        <v>-0.04459459459459459</v>
       </c>
       <c r="J2">
-        <v>-0.5132743362831858</v>
+        <v>-0.04459459459459459</v>
       </c>
       <c r="K2">
-        <v>-0.169</v>
+        <v>-0.047</v>
       </c>
       <c r="L2">
-        <v>-0.4985250737463127</v>
+        <v>-0.02117117117117117</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="V2">
-        <v>0.004095238095238094</v>
+        <v>0.004</v>
       </c>
       <c r="W2">
-        <v>-0.1005952380952381</v>
+        <v>-0.03587786259541985</v>
       </c>
       <c r="X2">
-        <v>0.1318382527368498</v>
+        <v>0.1175334866380634</v>
       </c>
       <c r="Y2">
-        <v>-0.2324334908320879</v>
+        <v>-0.1534113492334833</v>
       </c>
       <c r="Z2">
-        <v>0.4335038363171357</v>
+        <v>1.365313653136531</v>
       </c>
       <c r="AA2">
-        <v>-0.2225063938618926</v>
+        <v>-0.06088560885608856</v>
       </c>
       <c r="AB2">
-        <v>0.1298111297839653</v>
+        <v>0.1110570860062265</v>
       </c>
       <c r="AC2">
-        <v>-0.3523175236458579</v>
+        <v>-0.1719426948623151</v>
       </c>
       <c r="AD2">
-        <v>0.359</v>
+        <v>0.979</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.359</v>
+        <v>0.979</v>
       </c>
       <c r="AG2">
-        <v>0.316</v>
+        <v>0.949</v>
       </c>
       <c r="AH2">
-        <v>0.03306013445068606</v>
+        <v>0.1154617289774738</v>
       </c>
       <c r="AI2">
-        <v>0.2150988615937687</v>
+        <v>0.4258373205741627</v>
       </c>
       <c r="AJ2">
-        <v>0.02921597633136095</v>
+        <v>0.1123209847319209</v>
       </c>
       <c r="AK2">
-        <v>0.1943419434194342</v>
+        <v>0.4182459233142353</v>
       </c>
       <c r="AL2">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="AM2">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="AN2">
-        <v>-3.324074074074074</v>
+        <v>-19.19607843137255</v>
       </c>
       <c r="AO2">
-        <v>-19.33333333333333</v>
+        <v>-3.807692307692308</v>
       </c>
       <c r="AP2">
-        <v>-2.925925925925926</v>
+        <v>-18.6078431372549</v>
       </c>
       <c r="AQ2">
-        <v>-21.75</v>
+        <v>-3.807692307692308</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.2359882005899705</v>
+        <v>-0.05765765765765765</v>
       </c>
       <c r="H3">
-        <v>-0.2359882005899705</v>
+        <v>-0.05765765765765765</v>
       </c>
       <c r="I3">
-        <v>-0.5132743362831858</v>
+        <v>-0.04459459459459459</v>
       </c>
       <c r="J3">
-        <v>-0.5132743362831858</v>
+        <v>-0.04459459459459459</v>
       </c>
       <c r="K3">
-        <v>-0.169</v>
+        <v>-0.047</v>
       </c>
       <c r="L3">
-        <v>-0.4985250737463127</v>
+        <v>-0.02117117117117117</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.043</v>
+        <v>0.03</v>
       </c>
       <c r="V3">
-        <v>0.004095238095238094</v>
+        <v>0.004</v>
       </c>
       <c r="W3">
-        <v>-0.1005952380952381</v>
+        <v>-0.03587786259541985</v>
       </c>
       <c r="X3">
-        <v>0.1318382527368498</v>
+        <v>0.1175334866380634</v>
       </c>
       <c r="Y3">
-        <v>-0.2324334908320879</v>
+        <v>-0.1534113492334833</v>
       </c>
       <c r="Z3">
-        <v>0.4335038363171357</v>
+        <v>1.365313653136531</v>
       </c>
       <c r="AA3">
-        <v>-0.2225063938618926</v>
+        <v>-0.06088560885608856</v>
       </c>
       <c r="AB3">
-        <v>0.1298111297839653</v>
+        <v>0.1110570860062265</v>
       </c>
       <c r="AC3">
-        <v>-0.3523175236458579</v>
+        <v>-0.1719426948623151</v>
       </c>
       <c r="AD3">
-        <v>0.359</v>
+        <v>0.979</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.359</v>
+        <v>0.979</v>
       </c>
       <c r="AG3">
-        <v>0.316</v>
+        <v>0.949</v>
       </c>
       <c r="AH3">
-        <v>0.03306013445068606</v>
+        <v>0.1154617289774738</v>
       </c>
       <c r="AI3">
-        <v>0.2150988615937687</v>
+        <v>0.4258373205741627</v>
       </c>
       <c r="AJ3">
-        <v>0.02921597633136095</v>
+        <v>0.1123209847319209</v>
       </c>
       <c r="AK3">
-        <v>0.1943419434194342</v>
+        <v>0.4182459233142353</v>
       </c>
       <c r="AL3">
-        <v>0.008999999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="AM3">
-        <v>0.008</v>
+        <v>0.026</v>
       </c>
       <c r="AN3">
-        <v>-3.324074074074074</v>
+        <v>-19.19607843137255</v>
       </c>
       <c r="AO3">
-        <v>-19.33333333333333</v>
+        <v>-3.807692307692308</v>
       </c>
       <c r="AP3">
-        <v>-2.925925925925926</v>
+        <v>-18.6078431372549</v>
       </c>
       <c r="AQ3">
-        <v>-21.75</v>
+        <v>-3.807692307692308</v>
       </c>
     </row>
   </sheetData>
